--- a/Result/profitability/2440.xlsx
+++ b/Result/profitability/2440.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07875</v>
+        <v>-0.06875000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4875</v>
+        <v>4.48625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0425</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5.785</v>
+        <v>5.7425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0225</v>
+        <v>0.02625</v>
       </c>
       <c r="N4" t="n">
-        <v>6.02875</v>
+        <v>5.99875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.365</v>
+        <v>-0.335</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1575</v>
+        <v>-1.21875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.315</v>
+        <v>-0.30375</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3912500000000003</v>
+        <v>0.4775</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2875</v>
+        <v>-0.28625</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4675</v>
+        <v>2.41125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2625</v>
+        <v>-0.2762500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>4.143750000000001</v>
+        <v>3.86875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.27875</v>
       </c>
       <c r="N12" t="n">
-        <v>6.74875</v>
+        <v>6.748750000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9846,6 +9846,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1206</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1162</v>
+      </c>
+      <c r="E75" t="n">
+        <v>44</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.05499999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7857142857142858</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.374787052810903</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4900000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1177884615384616</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
